--- a/samples/법정교육_1_이수현황서식.xlsx
+++ b/samples/법정교육_1_이수현황서식.xlsx
@@ -4301,8 +4301,21 @@
       <c r="A9" s="24">
         <v>1</v>
       </c>
-      <c r="B9" s="24"/>
-      <c r="C9" s="10"/>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>행정지원과</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>교육행정7급</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>김가나</t>
+        </is>
+      </c>
       <c r="E9" s="29"/>
       <c r="F9" s="29"/>
       <c r="G9" s="28"/>
@@ -4321,9 +4334,21 @@
       <c r="A10" s="24">
         <v>2</v>
       </c>
-      <c r="B10" s="24"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="27"/>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>행정지원과</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>교육행정8급</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>이다라</t>
+        </is>
+      </c>
       <c r="E10" s="31"/>
       <c r="F10" s="16"/>
       <c r="G10" s="10"/>
@@ -4342,9 +4367,21 @@
       <c r="A11" s="24">
         <v>3</v>
       </c>
-      <c r="B11" s="24"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="27"/>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>행정지원과</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>교육행정6급</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>박마바</t>
+        </is>
+      </c>
       <c r="E11" s="16"/>
       <c r="F11" s="16"/>
       <c r="G11" s="10"/>
@@ -4363,9 +4400,21 @@
       <c r="A12" s="24">
         <v>4</v>
       </c>
-      <c r="B12" s="24"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="27"/>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>행정지원과</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>장학사</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>정자차</t>
+        </is>
+      </c>
       <c r="E12" s="31"/>
       <c r="F12" s="16"/>
       <c r="G12" s="10"/>
